--- a/data/기온예측.xlsx
+++ b/data/기온예측.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\user\Desktop\0. 마케팅기획팀\2025\0. 스터디\2025\streamlit_study\사업계획_공급량예측_상품별\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\user\Desktop\0. 마케팅기획팀\2026\0. 스터디\2026\streamlit_study\사업계획_공급량예측_상품별\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A73362F2-ADDC-47A7-A00E-A579B358206D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69D57FBF-A05B-4964-BCAC-76EEA9FBE99E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C90C0E77-5868-47F7-AD40-447DEE8C1EB1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C90C0E77-5868-47F7-AD40-447DEE8C1EB1}"/>
   </bookViews>
   <sheets>
     <sheet name="기온예측" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.0"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -88,8 +88,23 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -128,17 +143,38 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor rgb="FFD0CECE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="dotted">
+        <color rgb="FF000000"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -147,7 +183,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -187,7 +223,13 @@
     <xf numFmtId="2" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -524,7 +566,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AB07CAA-0875-49B7-8BEC-CB688CAA6154}">
-  <dimension ref="A1:C5819"/>
+  <dimension ref="A1:Q5819"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
@@ -2466,7 +2508,7 @@
       </c>
       <c r="C240" s="5"/>
     </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A241" s="4">
         <v>45627</v>
       </c>
@@ -2475,7 +2517,7 @@
       </c>
       <c r="C241" s="5"/>
     </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A242" s="6">
         <v>45658</v>
       </c>
@@ -2483,7 +2525,7 @@
         <v>1.3580645161290323</v>
       </c>
     </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A243" s="4">
         <v>45689</v>
       </c>
@@ -2491,7 +2533,7 @@
         <v>1.2249999999999999</v>
       </c>
     </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A244" s="6">
         <v>45717</v>
       </c>
@@ -2499,7 +2541,7 @@
         <v>9.5580645161290327</v>
       </c>
     </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A245" s="6">
         <v>45748</v>
       </c>
@@ -2507,7 +2549,7 @@
         <v>14.893333333333333</v>
       </c>
     </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A246" s="4">
         <v>45778</v>
       </c>
@@ -2515,7 +2557,7 @@
         <v>18.132258064516133</v>
       </c>
     </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A247" s="6">
         <v>45809</v>
       </c>
@@ -2523,7 +2565,7 @@
         <v>24.810000000000002</v>
       </c>
     </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A248" s="6">
         <v>45839</v>
       </c>
@@ -2531,7 +2573,7 @@
         <v>27.980645161290319</v>
       </c>
     </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A249" s="4">
         <v>45870</v>
       </c>
@@ -2539,7 +2581,7 @@
         <v>28.754838709677411</v>
       </c>
     </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A250" s="6">
         <v>45901</v>
       </c>
@@ -2547,7 +2589,7 @@
         <v>25.44</v>
       </c>
     </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A251" s="6">
         <v>45931</v>
       </c>
@@ -2555,7 +2597,7 @@
         <v>17.000000000000004</v>
       </c>
     </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A252" s="4">
         <v>45962</v>
       </c>
@@ -2563,7 +2605,7 @@
         <v>10.650000000000002</v>
       </c>
     </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A253" s="6">
         <v>45992</v>
       </c>
@@ -2571,34 +2613,70 @@
         <v>3.4677419354838714</v>
       </c>
     </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A254" s="6">
         <v>46023</v>
       </c>
-      <c r="B254" s="13">
-        <v>1.5301075268817204</v>
+      <c r="B254" s="15">
+        <v>1.1000000000000001</v>
       </c>
       <c r="C254" s="11">
         <v>1.831</v>
       </c>
-    </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="F254" s="13">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="G254" s="13">
+        <v>4.7</v>
+      </c>
+      <c r="H254" s="13">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="I254" s="13">
+        <v>15</v>
+      </c>
+      <c r="J254" s="13">
+        <v>19.100000000000001</v>
+      </c>
+      <c r="K254" s="13">
+        <v>24.4</v>
+      </c>
+      <c r="L254" s="13">
+        <v>27.2</v>
+      </c>
+      <c r="M254" s="13">
+        <v>27.9</v>
+      </c>
+      <c r="N254" s="14">
+        <v>22.5</v>
+      </c>
+      <c r="O254" s="13">
+        <v>16</v>
+      </c>
+      <c r="P254" s="13">
+        <v>10</v>
+      </c>
+      <c r="Q254" s="13">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="255" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A255" s="4">
         <v>46054</v>
       </c>
-      <c r="B255" s="13">
-        <v>3.6761494252873557</v>
+      <c r="B255" s="15">
+        <v>4.7</v>
       </c>
       <c r="C255" s="11">
         <v>3.6059999999999999</v>
       </c>
     </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A256" s="6">
         <v>46082</v>
       </c>
-      <c r="B256" s="13">
-        <v>9.9612903225806466</v>
+      <c r="B256" s="15">
+        <v>9.8000000000000007</v>
       </c>
       <c r="C256" s="11">
         <v>10.356</v>
@@ -2608,8 +2686,8 @@
       <c r="A257" s="6">
         <v>46113</v>
       </c>
-      <c r="B257" s="13">
-        <v>15.315555555555553</v>
+      <c r="B257" s="15">
+        <v>15</v>
       </c>
       <c r="C257" s="11">
         <v>15.930999999999999</v>
@@ -2619,8 +2697,8 @@
       <c r="A258" s="4">
         <v>46143</v>
       </c>
-      <c r="B258" s="13">
-        <v>18.938709677419357</v>
+      <c r="B258" s="15">
+        <v>19.100000000000001</v>
       </c>
       <c r="C258" s="11">
         <v>19.831</v>
@@ -2630,8 +2708,8 @@
       <c r="A259" s="6">
         <v>46174</v>
       </c>
-      <c r="B259" s="13">
-        <v>24.47</v>
+      <c r="B259" s="15">
+        <v>24.4</v>
       </c>
       <c r="C259" s="11">
         <v>24.881</v>
@@ -2641,8 +2719,8 @@
       <c r="A260" s="6">
         <v>46204</v>
       </c>
-      <c r="B260" s="13">
-        <v>27.497849462365593</v>
+      <c r="B260" s="15">
+        <v>27.2</v>
       </c>
       <c r="C260" s="11">
         <v>27.956</v>
@@ -2652,8 +2730,8 @@
       <c r="A261" s="4">
         <v>46235</v>
       </c>
-      <c r="B261" s="13">
-        <v>28.44086021505376</v>
+      <c r="B261" s="15">
+        <v>27.9</v>
       </c>
       <c r="C261" s="11">
         <v>28.530999999999999</v>
@@ -2663,8 +2741,8 @@
       <c r="A262" s="6">
         <v>46266</v>
       </c>
-      <c r="B262" s="13">
-        <v>24.793333333333333</v>
+      <c r="B262" s="15">
+        <v>22.5</v>
       </c>
       <c r="C262" s="11">
         <v>24.146999999999998</v>
@@ -2674,8 +2752,8 @@
       <c r="A263" s="6">
         <v>46296</v>
       </c>
-      <c r="B263" s="13">
-        <v>16.633333333333336</v>
+      <c r="B263" s="15">
+        <v>16</v>
       </c>
       <c r="C263" s="11">
         <v>16.68</v>
@@ -2685,8 +2763,8 @@
       <c r="A264" s="4">
         <v>46327</v>
       </c>
-      <c r="B264" s="13">
-        <v>10.166666666666668</v>
+      <c r="B264" s="15">
+        <v>10</v>
       </c>
       <c r="C264" s="11">
         <v>10.847</v>
@@ -2696,8 +2774,8 @@
       <c r="A265" s="6">
         <v>46357</v>
       </c>
-      <c r="B265" s="13">
-        <v>3.4784946236559144</v>
+      <c r="B265" s="15">
+        <v>2.4</v>
       </c>
       <c r="C265" s="11">
         <v>3.0139999999999998</v>

--- a/data/기온예측.xlsx
+++ b/data/기온예측.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\user\Desktop\0. 마케팅기획팀\2026\0. 스터디\2026\streamlit_study\사업계획_공급량예측_상품별\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69D57FBF-A05B-4964-BCAC-76EEA9FBE99E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CDA194F-D3AF-4D29-A1D0-6DD8104D8904}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C90C0E77-5868-47F7-AD40-447DEE8C1EB1}"/>
+    <workbookView xWindow="-28920" yWindow="3900" windowWidth="29040" windowHeight="15720" xr2:uid="{C90C0E77-5868-47F7-AD40-447DEE8C1EB1}"/>
   </bookViews>
   <sheets>
     <sheet name="기온예측" sheetId="1" r:id="rId1"/>
@@ -229,7 +229,7 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -572,6 +572,9 @@
     <col min="1" max="1" width="21" customWidth="1"/>
     <col min="2" max="2" width="15.75" style="2" customWidth="1"/>
     <col min="3" max="3" width="21.875" customWidth="1"/>
+    <col min="6" max="8" width="11" bestFit="1" customWidth="1"/>
+    <col min="9" max="15" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -2618,47 +2621,23 @@
         <v>46023</v>
       </c>
       <c r="B254" s="15">
-        <v>1.1000000000000001</v>
+        <v>1.0526881720430108</v>
       </c>
       <c r="C254" s="11">
         <v>1.831</v>
       </c>
-      <c r="F254" s="13">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="G254" s="13">
-        <v>4.7</v>
-      </c>
-      <c r="H254" s="13">
-        <v>9.8000000000000007</v>
-      </c>
-      <c r="I254" s="13">
-        <v>15</v>
-      </c>
-      <c r="J254" s="13">
-        <v>19.100000000000001</v>
-      </c>
-      <c r="K254" s="13">
-        <v>24.4</v>
-      </c>
-      <c r="L254" s="13">
-        <v>27.2</v>
-      </c>
-      <c r="M254" s="13">
-        <v>27.9</v>
-      </c>
-      <c r="N254" s="14">
-        <v>22.5</v>
-      </c>
-      <c r="O254" s="13">
-        <v>16</v>
-      </c>
-      <c r="P254" s="13">
-        <v>10</v>
-      </c>
-      <c r="Q254" s="13">
-        <v>2.4</v>
-      </c>
+      <c r="F254" s="13"/>
+      <c r="G254" s="13"/>
+      <c r="H254" s="13"/>
+      <c r="I254" s="13"/>
+      <c r="J254" s="13"/>
+      <c r="K254" s="13"/>
+      <c r="L254" s="13"/>
+      <c r="M254" s="13"/>
+      <c r="N254" s="14"/>
+      <c r="O254" s="13"/>
+      <c r="P254" s="13"/>
+      <c r="Q254" s="13"/>
     </row>
     <row r="255" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A255" s="4">
@@ -2670,13 +2649,25 @@
       <c r="C255" s="11">
         <v>3.6059999999999999</v>
       </c>
+      <c r="F255" s="7"/>
+      <c r="G255" s="7"/>
+      <c r="H255" s="7"/>
+      <c r="I255" s="7"/>
+      <c r="J255" s="7"/>
+      <c r="K255" s="7"/>
+      <c r="L255" s="7"/>
+      <c r="M255" s="7"/>
+      <c r="N255" s="7"/>
+      <c r="O255" s="7"/>
+      <c r="P255" s="7"/>
+      <c r="Q255" s="7"/>
     </row>
     <row r="256" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A256" s="6">
         <v>46082</v>
       </c>
       <c r="B256" s="15">
-        <v>9.8000000000000007</v>
+        <v>9.8193548387096765</v>
       </c>
       <c r="C256" s="11">
         <v>10.356</v>
@@ -2687,7 +2678,7 @@
         <v>46113</v>
       </c>
       <c r="B257" s="15">
-        <v>15</v>
+        <v>15.023333333333333</v>
       </c>
       <c r="C257" s="11">
         <v>15.930999999999999</v>
@@ -2698,7 +2689,7 @@
         <v>46143</v>
       </c>
       <c r="B258" s="15">
-        <v>19.100000000000001</v>
+        <v>19.095967741935485</v>
       </c>
       <c r="C258" s="11">
         <v>19.831</v>
@@ -2709,7 +2700,7 @@
         <v>46174</v>
       </c>
       <c r="B259" s="15">
-        <v>24.4</v>
+        <v>24.349999999999998</v>
       </c>
       <c r="C259" s="11">
         <v>24.881</v>
@@ -2720,7 +2711,7 @@
         <v>46204</v>
       </c>
       <c r="B260" s="15">
-        <v>27.2</v>
+        <v>27.228225806451615</v>
       </c>
       <c r="C260" s="11">
         <v>27.956</v>
@@ -2731,7 +2722,7 @@
         <v>46235</v>
       </c>
       <c r="B261" s="15">
-        <v>27.9</v>
+        <v>27.938709677419354</v>
       </c>
       <c r="C261" s="11">
         <v>28.530999999999999</v>
@@ -2742,7 +2733,7 @@
         <v>46266</v>
       </c>
       <c r="B262" s="15">
-        <v>22.5</v>
+        <v>22.85</v>
       </c>
       <c r="C262" s="11">
         <v>24.146999999999998</v>
@@ -2753,7 +2744,7 @@
         <v>46296</v>
       </c>
       <c r="B263" s="15">
-        <v>16</v>
+        <v>15.966666666666667</v>
       </c>
       <c r="C263" s="11">
         <v>16.68</v>
@@ -2764,7 +2755,7 @@
         <v>46327</v>
       </c>
       <c r="B264" s="15">
-        <v>10</v>
+        <v>9.8625000000000007</v>
       </c>
       <c r="C264" s="11">
         <v>10.847</v>
@@ -2775,7 +2766,7 @@
         <v>46357</v>
       </c>
       <c r="B265" s="15">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="C265" s="11">
         <v>3.0139999999999998</v>

--- a/data/기온예측.xlsx
+++ b/data/기온예측.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\user\Desktop\0. 마케팅기획팀\2026\0. 스터디\2026\streamlit_study\사업계획_공급량예측_상품별\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CDA194F-D3AF-4D29-A1D0-6DD8104D8904}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CB43531-FB2A-49A6-BA09-A48BE78CF21A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="3900" windowWidth="29040" windowHeight="15720" xr2:uid="{C90C0E77-5868-47F7-AD40-447DEE8C1EB1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C90C0E77-5868-47F7-AD40-447DEE8C1EB1}"/>
   </bookViews>
   <sheets>
     <sheet name="기온예측" sheetId="1" r:id="rId1"/>
@@ -2621,7 +2621,7 @@
         <v>46023</v>
       </c>
       <c r="B254" s="15">
-        <v>1.0526881720430108</v>
+        <v>1.5301075268817204</v>
       </c>
       <c r="C254" s="11">
         <v>1.831</v>
@@ -2644,7 +2644,7 @@
         <v>46054</v>
       </c>
       <c r="B255" s="15">
-        <v>4.7</v>
+        <v>3.6761494252873557</v>
       </c>
       <c r="C255" s="11">
         <v>3.6059999999999999</v>
@@ -2667,7 +2667,7 @@
         <v>46082</v>
       </c>
       <c r="B256" s="15">
-        <v>9.8193548387096765</v>
+        <v>9.9612903225806466</v>
       </c>
       <c r="C256" s="11">
         <v>10.356</v>
@@ -2678,7 +2678,7 @@
         <v>46113</v>
       </c>
       <c r="B257" s="15">
-        <v>15.023333333333333</v>
+        <v>15.315555555555553</v>
       </c>
       <c r="C257" s="11">
         <v>15.930999999999999</v>
@@ -2689,7 +2689,7 @@
         <v>46143</v>
       </c>
       <c r="B258" s="15">
-        <v>19.095967741935485</v>
+        <v>18.938709677419357</v>
       </c>
       <c r="C258" s="11">
         <v>19.831</v>
@@ -2700,7 +2700,7 @@
         <v>46174</v>
       </c>
       <c r="B259" s="15">
-        <v>24.349999999999998</v>
+        <v>24.47</v>
       </c>
       <c r="C259" s="11">
         <v>24.881</v>
@@ -2711,7 +2711,7 @@
         <v>46204</v>
       </c>
       <c r="B260" s="15">
-        <v>27.228225806451615</v>
+        <v>27.497849462365593</v>
       </c>
       <c r="C260" s="11">
         <v>27.956</v>
@@ -2722,7 +2722,7 @@
         <v>46235</v>
       </c>
       <c r="B261" s="15">
-        <v>27.938709677419354</v>
+        <v>28.44086021505376</v>
       </c>
       <c r="C261" s="11">
         <v>28.530999999999999</v>
@@ -2733,7 +2733,7 @@
         <v>46266</v>
       </c>
       <c r="B262" s="15">
-        <v>22.85</v>
+        <v>24.28</v>
       </c>
       <c r="C262" s="11">
         <v>24.146999999999998</v>
@@ -2744,7 +2744,7 @@
         <v>46296</v>
       </c>
       <c r="B263" s="15">
-        <v>15.966666666666667</v>
+        <v>16.766666666666669</v>
       </c>
       <c r="C263" s="11">
         <v>16.68</v>
@@ -2755,7 +2755,7 @@
         <v>46327</v>
       </c>
       <c r="B264" s="15">
-        <v>9.8625000000000007</v>
+        <v>9.8166666666666682</v>
       </c>
       <c r="C264" s="11">
         <v>10.847</v>
@@ -2766,7 +2766,7 @@
         <v>46357</v>
       </c>
       <c r="B265" s="15">
-        <v>2.35</v>
+        <v>3.4784946236559144</v>
       </c>
       <c r="C265" s="11">
         <v>3.0139999999999998</v>

--- a/data/기온예측.xlsx
+++ b/data/기온예측.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\user\Desktop\0. 마케팅기획팀\2026\0. 스터디\2026\streamlit_study\사업계획_공급량예측_상품별\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CB43531-FB2A-49A6-BA09-A48BE78CF21A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42FB6CC5-BFB0-43C8-B77F-7B7D5D93762F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C90C0E77-5868-47F7-AD40-447DEE8C1EB1}"/>
+    <workbookView xWindow="-28920" yWindow="3900" windowWidth="29040" windowHeight="15720" xr2:uid="{C90C0E77-5868-47F7-AD40-447DEE8C1EB1}"/>
   </bookViews>
   <sheets>
     <sheet name="기온예측" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>날짜</t>
   </si>
@@ -46,6 +46,22 @@
   </si>
   <si>
     <t>추세분석(지수평활법)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1~4월</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>실제기온</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5~12월</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3yav</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -104,7 +120,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -143,38 +159,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD0CECE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="dotted">
-        <color rgb="FF000000"/>
-      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -183,7 +178,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -223,13 +218,19 @@
     <xf numFmtId="2" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -566,7 +567,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AB07CAA-0875-49B7-8BEC-CB688CAA6154}">
-  <dimension ref="A1:Q5819"/>
+  <dimension ref="A1:R5819"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
@@ -2511,7 +2512,7 @@
       </c>
       <c r="C240" s="5"/>
     </row>
-    <row r="241" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A241" s="4">
         <v>45627</v>
       </c>
@@ -2520,7 +2521,7 @@
       </c>
       <c r="C241" s="5"/>
     </row>
-    <row r="242" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A242" s="6">
         <v>45658</v>
       </c>
@@ -2528,7 +2529,7 @@
         <v>1.3580645161290323</v>
       </c>
     </row>
-    <row r="243" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A243" s="4">
         <v>45689</v>
       </c>
@@ -2536,7 +2537,7 @@
         <v>1.2249999999999999</v>
       </c>
     </row>
-    <row r="244" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A244" s="6">
         <v>45717</v>
       </c>
@@ -2544,7 +2545,7 @@
         <v>9.5580645161290327</v>
       </c>
     </row>
-    <row r="245" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A245" s="6">
         <v>45748</v>
       </c>
@@ -2552,7 +2553,7 @@
         <v>14.893333333333333</v>
       </c>
     </row>
-    <row r="246" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A246" s="4">
         <v>45778</v>
       </c>
@@ -2560,7 +2561,7 @@
         <v>18.132258064516133</v>
       </c>
     </row>
-    <row r="247" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A247" s="6">
         <v>45809</v>
       </c>
@@ -2568,7 +2569,7 @@
         <v>24.810000000000002</v>
       </c>
     </row>
-    <row r="248" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A248" s="6">
         <v>45839</v>
       </c>
@@ -2576,7 +2577,7 @@
         <v>27.980645161290319</v>
       </c>
     </row>
-    <row r="249" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A249" s="4">
         <v>45870</v>
       </c>
@@ -2584,7 +2585,7 @@
         <v>28.754838709677411</v>
       </c>
     </row>
-    <row r="250" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A250" s="6">
         <v>45901</v>
       </c>
@@ -2592,7 +2593,7 @@
         <v>25.44</v>
       </c>
     </row>
-    <row r="251" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A251" s="6">
         <v>45931</v>
       </c>
@@ -2600,84 +2601,135 @@
         <v>17.000000000000004</v>
       </c>
     </row>
-    <row r="252" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A252" s="4">
         <v>45962</v>
       </c>
       <c r="B252" s="8">
         <v>10.650000000000002</v>
       </c>
-    </row>
-    <row r="253" spans="1:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="F252" s="14"/>
+      <c r="G252" s="14"/>
+      <c r="H252" s="14"/>
+      <c r="I252" s="14"/>
+      <c r="J252" s="14"/>
+      <c r="K252" s="14"/>
+      <c r="L252" s="14"/>
+      <c r="M252" s="14"/>
+      <c r="N252" s="14"/>
+      <c r="O252" s="14"/>
+      <c r="P252" s="14"/>
+      <c r="Q252" s="14"/>
+      <c r="R252" s="14"/>
+    </row>
+    <row r="253" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A253" s="6">
         <v>45992</v>
       </c>
       <c r="B253" s="8">
         <v>3.4677419354838714</v>
       </c>
-    </row>
-    <row r="254" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="F253" s="14"/>
+      <c r="G253" s="14"/>
+      <c r="H253" s="14"/>
+      <c r="I253" s="14"/>
+      <c r="J253" s="14"/>
+      <c r="K253" s="14"/>
+      <c r="L253" s="14"/>
+      <c r="M253" s="14"/>
+      <c r="N253" s="14"/>
+      <c r="O253" s="14"/>
+      <c r="P253" s="14"/>
+      <c r="Q253" s="14"/>
+      <c r="R253" s="14"/>
+    </row>
+    <row r="254" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A254" s="6">
         <v>46023</v>
       </c>
-      <c r="B254" s="15">
-        <v>1.5301075268817204</v>
+      <c r="B254" s="13">
+        <v>0.3</v>
       </c>
       <c r="C254" s="11">
         <v>1.831</v>
       </c>
-      <c r="F254" s="13"/>
-      <c r="G254" s="13"/>
-      <c r="H254" s="13"/>
-      <c r="I254" s="13"/>
-      <c r="J254" s="13"/>
-      <c r="K254" s="13"/>
-      <c r="L254" s="13"/>
-      <c r="M254" s="13"/>
-      <c r="N254" s="14"/>
-      <c r="O254" s="13"/>
-      <c r="P254" s="13"/>
-      <c r="Q254" s="13"/>
-    </row>
-    <row r="255" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="E254" t="s">
+        <v>3</v>
+      </c>
+      <c r="F254" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="G254" s="15"/>
+      <c r="H254" s="15"/>
+      <c r="I254" s="15"/>
+      <c r="J254" s="15"/>
+      <c r="K254" s="15"/>
+      <c r="L254" s="15"/>
+      <c r="M254" s="15"/>
+      <c r="N254" s="16"/>
+      <c r="O254" s="15"/>
+      <c r="P254" s="15"/>
+      <c r="Q254" s="15"/>
+      <c r="R254" s="14"/>
+    </row>
+    <row r="255" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A255" s="4">
         <v>46054</v>
       </c>
-      <c r="B255" s="15">
-        <v>3.6761494252873557</v>
+      <c r="B255" s="13">
+        <v>4.3</v>
       </c>
       <c r="C255" s="11">
         <v>3.6059999999999999</v>
       </c>
-      <c r="F255" s="7"/>
-      <c r="G255" s="7"/>
-      <c r="H255" s="7"/>
-      <c r="I255" s="7"/>
-      <c r="J255" s="7"/>
-      <c r="K255" s="7"/>
-      <c r="L255" s="7"/>
-      <c r="M255" s="7"/>
-      <c r="N255" s="7"/>
-      <c r="O255" s="7"/>
-      <c r="P255" s="7"/>
-      <c r="Q255" s="7"/>
-    </row>
-    <row r="256" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="E255" t="s">
+        <v>5</v>
+      </c>
+      <c r="F255" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="G255" s="17"/>
+      <c r="H255" s="17"/>
+      <c r="I255" s="17"/>
+      <c r="J255" s="17"/>
+      <c r="K255" s="17"/>
+      <c r="L255" s="17"/>
+      <c r="M255" s="17"/>
+      <c r="N255" s="17"/>
+      <c r="O255" s="17"/>
+      <c r="P255" s="17"/>
+      <c r="Q255" s="17"/>
+      <c r="R255" s="14"/>
+    </row>
+    <row r="256" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A256" s="6">
         <v>46082</v>
       </c>
-      <c r="B256" s="15">
-        <v>9.9612903225806466</v>
+      <c r="B256" s="13">
+        <v>9.3000000000000007</v>
       </c>
       <c r="C256" s="11">
         <v>10.356</v>
       </c>
+      <c r="F256" s="14"/>
+      <c r="G256" s="14"/>
+      <c r="H256" s="14"/>
+      <c r="I256" s="14"/>
+      <c r="J256" s="14"/>
+      <c r="K256" s="14"/>
+      <c r="L256" s="14"/>
+      <c r="M256" s="14"/>
+      <c r="N256" s="14"/>
+      <c r="O256" s="14"/>
+      <c r="P256" s="14"/>
+      <c r="Q256" s="14"/>
+      <c r="R256" s="14"/>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A257" s="6">
         <v>46113</v>
       </c>
-      <c r="B257" s="15">
+      <c r="B257" s="13">
         <v>15.315555555555553</v>
       </c>
       <c r="C257" s="11">
@@ -2688,7 +2740,7 @@
       <c r="A258" s="4">
         <v>46143</v>
       </c>
-      <c r="B258" s="15">
+      <c r="B258" s="13">
         <v>18.938709677419357</v>
       </c>
       <c r="C258" s="11">
@@ -2699,7 +2751,7 @@
       <c r="A259" s="6">
         <v>46174</v>
       </c>
-      <c r="B259" s="15">
+      <c r="B259" s="13">
         <v>24.47</v>
       </c>
       <c r="C259" s="11">
@@ -2710,7 +2762,7 @@
       <c r="A260" s="6">
         <v>46204</v>
       </c>
-      <c r="B260" s="15">
+      <c r="B260" s="13">
         <v>27.497849462365593</v>
       </c>
       <c r="C260" s="11">
@@ -2721,7 +2773,7 @@
       <c r="A261" s="4">
         <v>46235</v>
       </c>
-      <c r="B261" s="15">
+      <c r="B261" s="13">
         <v>28.44086021505376</v>
       </c>
       <c r="C261" s="11">
@@ -2732,7 +2784,7 @@
       <c r="A262" s="6">
         <v>46266</v>
       </c>
-      <c r="B262" s="15">
+      <c r="B262" s="13">
         <v>24.28</v>
       </c>
       <c r="C262" s="11">
@@ -2743,7 +2795,7 @@
       <c r="A263" s="6">
         <v>46296</v>
       </c>
-      <c r="B263" s="15">
+      <c r="B263" s="13">
         <v>16.766666666666669</v>
       </c>
       <c r="C263" s="11">
@@ -2754,7 +2806,7 @@
       <c r="A264" s="4">
         <v>46327</v>
       </c>
-      <c r="B264" s="15">
+      <c r="B264" s="13">
         <v>9.8166666666666682</v>
       </c>
       <c r="C264" s="11">
@@ -2765,7 +2817,7 @@
       <c r="A265" s="6">
         <v>46357</v>
       </c>
-      <c r="B265" s="15">
+      <c r="B265" s="13">
         <v>3.4784946236559144</v>
       </c>
       <c r="C265" s="11">

--- a/data/기온예측.xlsx
+++ b/data/기온예측.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\user\Desktop\0. 마케팅기획팀\2026\0. 스터디\2026\streamlit_study\사업계획_공급량예측_상품별\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42FB6CC5-BFB0-43C8-B77F-7B7D5D93762F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CB36EAD-7C45-4CBD-A0B1-34825C85DC14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="3900" windowWidth="29040" windowHeight="15720" xr2:uid="{C90C0E77-5868-47F7-AD40-447DEE8C1EB1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C90C0E77-5868-47F7-AD40-447DEE8C1EB1}"/>
   </bookViews>
   <sheets>
     <sheet name="기온예측" sheetId="1" r:id="rId1"/>
@@ -221,16 +221,16 @@
     <xf numFmtId="176" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2651,7 +2651,7 @@
         <v>0.3</v>
       </c>
       <c r="C254" s="11">
-        <v>1.831</v>
+        <v>1.8</v>
       </c>
       <c r="E254" t="s">
         <v>3</v>
@@ -2680,7 +2680,7 @@
         <v>4.3</v>
       </c>
       <c r="C255" s="11">
-        <v>3.6059999999999999</v>
+        <v>3.6</v>
       </c>
       <c r="E255" t="s">
         <v>5</v>
@@ -2709,7 +2709,7 @@
         <v>9.3000000000000007</v>
       </c>
       <c r="C256" s="11">
-        <v>10.356</v>
+        <v>10.3</v>
       </c>
       <c r="F256" s="14"/>
       <c r="G256" s="14"/>
@@ -2733,7 +2733,7 @@
         <v>15.315555555555553</v>
       </c>
       <c r="C257" s="11">
-        <v>15.930999999999999</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.3">
@@ -2744,7 +2744,7 @@
         <v>18.938709677419357</v>
       </c>
       <c r="C258" s="11">
-        <v>19.831</v>
+        <v>18.600000000000001</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.3">
@@ -2755,7 +2755,7 @@
         <v>24.47</v>
       </c>
       <c r="C259" s="11">
-        <v>24.881</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.3">
@@ -2766,7 +2766,7 @@
         <v>27.497849462365593</v>
       </c>
       <c r="C260" s="11">
-        <v>27.956</v>
+        <v>27.3</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.3">
@@ -2777,7 +2777,7 @@
         <v>28.44086021505376</v>
       </c>
       <c r="C261" s="11">
-        <v>28.530999999999999</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.3">
@@ -2788,7 +2788,7 @@
         <v>24.28</v>
       </c>
       <c r="C262" s="11">
-        <v>24.146999999999998</v>
+        <v>24.7</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.3">
@@ -2799,7 +2799,7 @@
         <v>16.766666666666669</v>
       </c>
       <c r="C263" s="11">
-        <v>16.68</v>
+        <v>17.100000000000001</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.3">
@@ -2810,7 +2810,7 @@
         <v>9.8166666666666682</v>
       </c>
       <c r="C264" s="11">
-        <v>10.847</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.3">
@@ -2821,7 +2821,7 @@
         <v>3.4784946236559144</v>
       </c>
       <c r="C265" s="11">
-        <v>3.0139999999999998</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.3">

--- a/data/기온예측.xlsx
+++ b/data/기온예측.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\user\Desktop\0. 마케팅기획팀\2026\0. 스터디\2026\streamlit_study\사업계획_공급량예측_상품별\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CB36EAD-7C45-4CBD-A0B1-34825C85DC14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC640285-D327-47D0-BBA2-3E6B079B1904}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C90C0E77-5868-47F7-AD40-447DEE8C1EB1}"/>
   </bookViews>
@@ -2648,7 +2648,7 @@
         <v>46023</v>
       </c>
       <c r="B254" s="13">
-        <v>0.3</v>
+        <v>1.052688172043011</v>
       </c>
       <c r="C254" s="11">
         <v>1.8</v>
@@ -2677,7 +2677,7 @@
         <v>46054</v>
       </c>
       <c r="B255" s="13">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="C255" s="11">
         <v>3.6</v>
@@ -2706,7 +2706,7 @@
         <v>46082</v>
       </c>
       <c r="B256" s="13">
-        <v>9.3000000000000007</v>
+        <v>9.8193548387096765</v>
       </c>
       <c r="C256" s="11">
         <v>10.3</v>
@@ -2730,7 +2730,7 @@
         <v>46113</v>
       </c>
       <c r="B257" s="13">
-        <v>15.315555555555553</v>
+        <v>15.02333333333333</v>
       </c>
       <c r="C257" s="11">
         <v>15.3</v>
@@ -2741,7 +2741,7 @@
         <v>46143</v>
       </c>
       <c r="B258" s="13">
-        <v>18.938709677419357</v>
+        <v>19.095967741935489</v>
       </c>
       <c r="C258" s="11">
         <v>18.600000000000001</v>
@@ -2752,7 +2752,7 @@
         <v>46174</v>
       </c>
       <c r="B259" s="13">
-        <v>24.47</v>
+        <v>24.35</v>
       </c>
       <c r="C259" s="11">
         <v>24.9</v>
@@ -2763,7 +2763,7 @@
         <v>46204</v>
       </c>
       <c r="B260" s="13">
-        <v>27.497849462365593</v>
+        <v>27.228225806451611</v>
       </c>
       <c r="C260" s="11">
         <v>27.3</v>
@@ -2774,7 +2774,7 @@
         <v>46235</v>
       </c>
       <c r="B261" s="13">
-        <v>28.44086021505376</v>
+        <v>27.93870967741935</v>
       </c>
       <c r="C261" s="11">
         <v>28.6</v>
@@ -2785,7 +2785,7 @@
         <v>46266</v>
       </c>
       <c r="B262" s="13">
-        <v>24.28</v>
+        <v>22.85</v>
       </c>
       <c r="C262" s="11">
         <v>24.7</v>
@@ -2796,7 +2796,7 @@
         <v>46296</v>
       </c>
       <c r="B263" s="13">
-        <v>16.766666666666669</v>
+        <v>15.96666666666667</v>
       </c>
       <c r="C263" s="11">
         <v>17.100000000000001</v>
@@ -2807,7 +2807,7 @@
         <v>46327</v>
       </c>
       <c r="B264" s="13">
-        <v>9.8166666666666682</v>
+        <v>9.8625000000000007</v>
       </c>
       <c r="C264" s="11">
         <v>10.6</v>
@@ -2818,7 +2818,7 @@
         <v>46357</v>
       </c>
       <c r="B265" s="13">
-        <v>3.4784946236559144</v>
+        <v>2.35</v>
       </c>
       <c r="C265" s="11">
         <v>3.6</v>

--- a/data/기온예측.xlsx
+++ b/data/기온예측.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\user\Desktop\0. 마케팅기획팀\2026\0. 스터디\2026\streamlit_study\사업계획_공급량예측_상품별\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC640285-D327-47D0-BBA2-3E6B079B1904}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6926CA5E-48CB-4D71-9083-2E01D2959C27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C90C0E77-5868-47F7-AD40-447DEE8C1EB1}"/>
   </bookViews>
@@ -69,10 +69,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="3">
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="176" formatCode="0.0"/>
+    <numFmt numFmtId="177" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -118,6 +120,14 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="8">
@@ -173,12 +183,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -233,8 +246,21 @@
     <xf numFmtId="176" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2648,7 +2674,7 @@
         <v>46023</v>
       </c>
       <c r="B254" s="13">
-        <v>1.052688172043011</v>
+        <v>0.3</v>
       </c>
       <c r="C254" s="11">
         <v>1.8</v>
@@ -2660,7 +2686,9 @@
         <v>4</v>
       </c>
       <c r="G254" s="15"/>
-      <c r="H254" s="15"/>
+      <c r="H254" s="18">
+        <v>1.052688172043011</v>
+      </c>
       <c r="I254" s="15"/>
       <c r="J254" s="15"/>
       <c r="K254" s="15"/>
@@ -2677,7 +2705,7 @@
         <v>46054</v>
       </c>
       <c r="B255" s="13">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="C255" s="11">
         <v>3.6</v>
@@ -2689,7 +2717,9 @@
         <v>6</v>
       </c>
       <c r="G255" s="17"/>
-      <c r="H255" s="17"/>
+      <c r="H255" s="19">
+        <v>4.7</v>
+      </c>
       <c r="I255" s="17"/>
       <c r="J255" s="17"/>
       <c r="K255" s="17"/>
@@ -2706,14 +2736,16 @@
         <v>46082</v>
       </c>
       <c r="B256" s="13">
-        <v>9.8193548387096765</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="C256" s="11">
         <v>10.3</v>
       </c>
       <c r="F256" s="14"/>
       <c r="G256" s="14"/>
-      <c r="H256" s="14"/>
+      <c r="H256" s="20">
+        <v>9.8193548387096765</v>
+      </c>
       <c r="I256" s="14"/>
       <c r="J256" s="14"/>
       <c r="K256" s="14"/>
@@ -2725,106 +2757,133 @@
       <c r="Q256" s="14"/>
       <c r="R256" s="14"/>
     </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A257" s="6">
         <v>46113</v>
       </c>
       <c r="B257" s="13">
-        <v>15.02333333333333</v>
+        <v>15.315555555555553</v>
       </c>
       <c r="C257" s="11">
         <v>15.3</v>
       </c>
-    </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="H257" s="21">
+        <v>15.02333333333333</v>
+      </c>
+    </row>
+    <row r="258" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A258" s="4">
         <v>46143</v>
       </c>
       <c r="B258" s="13">
-        <v>19.095967741935489</v>
+        <v>18.938709677419357</v>
       </c>
       <c r="C258" s="11">
         <v>18.600000000000001</v>
       </c>
-    </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="H258" s="21">
+        <v>19.095967741935489</v>
+      </c>
+    </row>
+    <row r="259" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A259" s="6">
         <v>46174</v>
       </c>
       <c r="B259" s="13">
-        <v>24.35</v>
+        <v>24.47</v>
       </c>
       <c r="C259" s="11">
         <v>24.9</v>
       </c>
-    </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="H259" s="21">
+        <v>24.35</v>
+      </c>
+    </row>
+    <row r="260" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A260" s="6">
         <v>46204</v>
       </c>
       <c r="B260" s="13">
-        <v>27.228225806451611</v>
+        <v>27.497849462365593</v>
       </c>
       <c r="C260" s="11">
         <v>27.3</v>
       </c>
-    </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="H260" s="21">
+        <v>27.228225806451611</v>
+      </c>
+    </row>
+    <row r="261" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A261" s="4">
         <v>46235</v>
       </c>
       <c r="B261" s="13">
-        <v>27.93870967741935</v>
+        <v>28.44086021505376</v>
       </c>
       <c r="C261" s="11">
         <v>28.6</v>
       </c>
-    </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="H261" s="21">
+        <v>27.93870967741935</v>
+      </c>
+    </row>
+    <row r="262" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A262" s="6">
         <v>46266</v>
       </c>
       <c r="B262" s="13">
-        <v>22.85</v>
+        <v>24.28</v>
       </c>
       <c r="C262" s="11">
         <v>24.7</v>
       </c>
-    </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="H262" s="21">
+        <v>22.85</v>
+      </c>
+    </row>
+    <row r="263" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A263" s="6">
         <v>46296</v>
       </c>
       <c r="B263" s="13">
-        <v>15.96666666666667</v>
+        <v>16.766666666666669</v>
       </c>
       <c r="C263" s="11">
         <v>17.100000000000001</v>
       </c>
-    </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="H263" s="21">
+        <v>15.96666666666667</v>
+      </c>
+    </row>
+    <row r="264" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A264" s="4">
         <v>46327</v>
       </c>
       <c r="B264" s="13">
-        <v>9.8625000000000007</v>
+        <v>9.8166666666666682</v>
       </c>
       <c r="C264" s="11">
         <v>10.6</v>
       </c>
-    </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="H264" s="21">
+        <v>9.8625000000000007</v>
+      </c>
+    </row>
+    <row r="265" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A265" s="6">
         <v>46357</v>
       </c>
       <c r="B265" s="13">
-        <v>2.35</v>
+        <v>3.4784946236559144</v>
       </c>
       <c r="C265" s="11">
         <v>3.6</v>
       </c>
-    </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="H265" s="21">
+        <v>2.35</v>
+      </c>
+    </row>
+    <row r="266" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A266" s="6">
         <v>46388</v>
       </c>
@@ -2835,7 +2894,7 @@
         <v>2.0129999999999999</v>
       </c>
     </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A267" s="4">
         <v>46419</v>
       </c>
@@ -2846,7 +2905,7 @@
         <v>3.7879999999999998</v>
       </c>
     </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A268" s="6">
         <v>46447</v>
       </c>
@@ -2857,7 +2916,7 @@
         <v>10.538</v>
       </c>
     </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A269" s="6">
         <v>46478</v>
       </c>
@@ -2868,7 +2927,7 @@
         <v>16.113</v>
       </c>
     </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A270" s="4">
         <v>46508</v>
       </c>
@@ -2879,7 +2938,7 @@
         <v>20.013000000000002</v>
       </c>
     </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A271" s="6">
         <v>46539</v>
       </c>
@@ -2890,7 +2949,7 @@
         <v>25.062999999999999</v>
       </c>
     </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A272" s="6">
         <v>46569</v>
       </c>

--- a/data/기온예측.xlsx
+++ b/data/기온예측.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\user\Desktop\0. 마케팅기획팀\2026\0. 스터디\2026\streamlit_study\사업계획_공급량예측_상품별\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6926CA5E-48CB-4D71-9083-2E01D2959C27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02177555-7201-4AEC-817B-7335B385370E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C90C0E77-5868-47F7-AD40-447DEE8C1EB1}"/>
+    <workbookView xWindow="-28920" yWindow="3900" windowWidth="29040" windowHeight="15720" xr2:uid="{C90C0E77-5868-47F7-AD40-447DEE8C1EB1}"/>
   </bookViews>
   <sheets>
     <sheet name="기온예측" sheetId="1" r:id="rId1"/>
@@ -49,19 +49,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1~4월</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>실제기온</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>5~12월</t>
+    <t>3yav</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>3yav</t>
+    <t>1~6월</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7~12월</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2680,15 +2680,13 @@
         <v>1.8</v>
       </c>
       <c r="E254" t="s">
+        <v>5</v>
+      </c>
+      <c r="F254" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="F254" s="15" t="s">
-        <v>4</v>
-      </c>
       <c r="G254" s="15"/>
-      <c r="H254" s="18">
-        <v>1.052688172043011</v>
-      </c>
+      <c r="H254" s="18"/>
       <c r="I254" s="15"/>
       <c r="J254" s="15"/>
       <c r="K254" s="15"/>
@@ -2711,15 +2709,13 @@
         <v>3.6</v>
       </c>
       <c r="E255" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F255" s="17" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G255" s="17"/>
-      <c r="H255" s="19">
-        <v>4.7</v>
-      </c>
+      <c r="H255" s="19"/>
       <c r="I255" s="17"/>
       <c r="J255" s="17"/>
       <c r="K255" s="17"/>
@@ -2743,9 +2739,7 @@
       </c>
       <c r="F256" s="14"/>
       <c r="G256" s="14"/>
-      <c r="H256" s="20">
-        <v>9.8193548387096765</v>
-      </c>
+      <c r="H256" s="20"/>
       <c r="I256" s="14"/>
       <c r="J256" s="14"/>
       <c r="K256" s="14"/>
@@ -2762,42 +2756,36 @@
         <v>46113</v>
       </c>
       <c r="B257" s="13">
-        <v>15.315555555555553</v>
+        <v>15.3</v>
       </c>
       <c r="C257" s="11">
         <v>15.3</v>
       </c>
-      <c r="H257" s="21">
-        <v>15.02333333333333</v>
-      </c>
+      <c r="H257" s="21"/>
     </row>
     <row r="258" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A258" s="4">
         <v>46143</v>
       </c>
       <c r="B258" s="13">
-        <v>18.938709677419357</v>
+        <v>20.3</v>
       </c>
       <c r="C258" s="11">
         <v>18.600000000000001</v>
       </c>
-      <c r="H258" s="21">
-        <v>19.095967741935489</v>
-      </c>
+      <c r="H258" s="21"/>
     </row>
     <row r="259" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A259" s="6">
         <v>46174</v>
       </c>
       <c r="B259" s="13">
-        <v>24.47</v>
+        <v>23.4</v>
       </c>
       <c r="C259" s="11">
         <v>24.9</v>
       </c>
-      <c r="H259" s="21">
-        <v>24.35</v>
-      </c>
+      <c r="H259" s="21"/>
     </row>
     <row r="260" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A260" s="6">
@@ -2809,9 +2797,7 @@
       <c r="C260" s="11">
         <v>27.3</v>
       </c>
-      <c r="H260" s="21">
-        <v>27.228225806451611</v>
-      </c>
+      <c r="H260" s="21"/>
     </row>
     <row r="261" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A261" s="4">
@@ -2823,9 +2809,7 @@
       <c r="C261" s="11">
         <v>28.6</v>
       </c>
-      <c r="H261" s="21">
-        <v>27.93870967741935</v>
-      </c>
+      <c r="H261" s="21"/>
     </row>
     <row r="262" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A262" s="6">
@@ -2837,9 +2821,7 @@
       <c r="C262" s="11">
         <v>24.7</v>
       </c>
-      <c r="H262" s="21">
-        <v>22.85</v>
-      </c>
+      <c r="H262" s="21"/>
     </row>
     <row r="263" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A263" s="6">
@@ -2851,9 +2833,7 @@
       <c r="C263" s="11">
         <v>17.100000000000001</v>
       </c>
-      <c r="H263" s="21">
-        <v>15.96666666666667</v>
-      </c>
+      <c r="H263" s="21"/>
     </row>
     <row r="264" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A264" s="4">
@@ -2865,9 +2845,7 @@
       <c r="C264" s="11">
         <v>10.6</v>
       </c>
-      <c r="H264" s="21">
-        <v>9.8625000000000007</v>
-      </c>
+      <c r="H264" s="21"/>
     </row>
     <row r="265" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A265" s="6">
@@ -2879,9 +2857,7 @@
       <c r="C265" s="11">
         <v>3.6</v>
       </c>
-      <c r="H265" s="21">
-        <v>2.35</v>
-      </c>
+      <c r="H265" s="21"/>
     </row>
     <row r="266" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A266" s="6">

--- a/data/기온예측.xlsx
+++ b/data/기온예측.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\user\Desktop\0. 마케팅기획팀\2026\0. 스터디\2026\streamlit_study\사업계획_공급량예측_상품별\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02177555-7201-4AEC-817B-7335B385370E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57536936-1AB8-492E-9D71-61F3FB4C5188}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="3900" windowWidth="29040" windowHeight="15720" xr2:uid="{C90C0E77-5868-47F7-AD40-447DEE8C1EB1}"/>
   </bookViews>
@@ -53,15 +53,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>3yav</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1~6월</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>7~12월</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5yav</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2680,7 +2680,7 @@
         <v>1.8</v>
       </c>
       <c r="E254" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F254" s="15" t="s">
         <v>3</v>
@@ -2709,10 +2709,10 @@
         <v>3.6</v>
       </c>
       <c r="E255" t="s">
+        <v>5</v>
+      </c>
+      <c r="F255" s="17" t="s">
         <v>6</v>
-      </c>
-      <c r="F255" s="17" t="s">
-        <v>4</v>
       </c>
       <c r="G255" s="17"/>
       <c r="H255" s="19"/>
@@ -2792,7 +2792,7 @@
         <v>46204</v>
       </c>
       <c r="B260" s="13">
-        <v>27.497849462365593</v>
+        <v>27.378709677419359</v>
       </c>
       <c r="C260" s="11">
         <v>27.3</v>
@@ -2804,7 +2804,7 @@
         <v>46235</v>
       </c>
       <c r="B261" s="13">
-        <v>28.44086021505376</v>
+        <v>27.584516129032256</v>
       </c>
       <c r="C261" s="11">
         <v>28.6</v>
@@ -2816,7 +2816,7 @@
         <v>46266</v>
       </c>
       <c r="B262" s="13">
-        <v>24.28</v>
+        <v>23.368000000000002</v>
       </c>
       <c r="C262" s="11">
         <v>24.7</v>
@@ -2828,7 +2828,7 @@
         <v>46296</v>
       </c>
       <c r="B263" s="13">
-        <v>16.766666666666669</v>
+        <v>16.46</v>
       </c>
       <c r="C263" s="11">
         <v>17.100000000000001</v>
@@ -2840,7 +2840,7 @@
         <v>46327</v>
       </c>
       <c r="B264" s="13">
-        <v>9.8166666666666682</v>
+        <v>9.99</v>
       </c>
       <c r="C264" s="11">
         <v>10.6</v>
@@ -2852,7 +2852,7 @@
         <v>46357</v>
       </c>
       <c r="B265" s="13">
-        <v>3.4784946236559144</v>
+        <v>2.7870967741935488</v>
       </c>
       <c r="C265" s="11">
         <v>3.6</v>
